--- a/artfynd/A 20533-2023 artfynd.xlsx
+++ b/artfynd/A 20533-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ11"/>
+  <dimension ref="A1:AZ18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -680,61 +680,49 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>110234754</v>
+        <v>110851340</v>
       </c>
       <c r="B2" t="n">
-        <v>57966</v>
+        <v>57879</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>100048</v>
+        <v>100034</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mindre hackspett</t>
+          <t>Blå kärrhök</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Dryobates minor</t>
+          <t>Circus cyaneus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>adult</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1766)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr"/>
+      <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>par i lämplig häckbiotop</t>
-        </is>
-      </c>
+      <c r="M2" t="inlineStr"/>
       <c r="N2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R2" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S2" t="n">
         <v>25</v>
@@ -761,22 +749,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>21:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -802,33 +790,33 @@
       <c r="AY2" t="inlineStr"/>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110234754</t>
+          <t>https://artportalen.se/Sighting/110851340</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>110221078</v>
+        <v>109849917</v>
       </c>
       <c r="B3" t="n">
-        <v>57950</v>
+        <v>57966</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100049</v>
+        <v>100048</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -836,25 +824,25 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
-      <c r="M3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
       <c r="N3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R3" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S3" t="n">
         <v>25</v>
@@ -881,12 +869,22 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2023-06-18</t>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AB3" t="inlineStr">
+        <is>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -912,49 +910,56 @@
       <c r="AY3" t="inlineStr"/>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110221078</t>
+          <t>https://artportalen.se/Sighting/109849917</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>110234764</v>
+        <v>110234754</v>
       </c>
       <c r="B4" t="n">
-        <v>8882</v>
+        <v>57966</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>100890</v>
+        <v>100048</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mulmknäppare</t>
+          <t>Mindre hackspett</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Elater ferrugineus</t>
+          <t>Dryobates minor</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr"/>
-      <c r="K4" t="inlineStr"/>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>adult</t>
+        </is>
+      </c>
       <c r="L4" t="inlineStr"/>
-      <c r="M4" t="inlineStr"/>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>par i lämplig häckbiotop</t>
+        </is>
+      </c>
       <c r="N4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
@@ -1016,7 +1021,6 @@
       <c r="AE4" t="b">
         <v>0</v>
       </c>
-      <c r="AF4" t="inlineStr"/>
       <c r="AG4" t="b">
         <v>0</v>
       </c>
@@ -1034,16 +1038,16 @@
       <c r="AY4" t="inlineStr"/>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110234764</t>
+          <t>https://artportalen.se/Sighting/110234754</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>110234790</v>
+        <v>110221078</v>
       </c>
       <c r="B5" t="n">
-        <v>9414</v>
+        <v>57950</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1051,16 +1055,16 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>105076</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Noshornsoxe</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sinodendron cylindricum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -1073,7 +1077,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J5" t="inlineStr"/>
       <c r="K5" t="inlineStr"/>
       <c r="L5" t="inlineStr"/>
       <c r="M5" t="inlineStr"/>
@@ -1114,22 +1117,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>16:24</t>
+          <t>2023-06-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1138,7 +1131,6 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
-      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
@@ -1156,59 +1148,55 @@
       <c r="AY5" t="inlineStr"/>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110234790</t>
+          <t>https://artportalen.se/Sighting/110221078</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>110221107</v>
+        <v>110851317</v>
       </c>
       <c r="B6" t="n">
-        <v>110078</v>
+        <v>57899</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E6" t="n">
-        <v>220299</v>
+        <v>100067</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Havsörn</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Haliaeetus albicilla</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
       <c r="K6" t="inlineStr"/>
       <c r="L6" t="inlineStr"/>
+      <c r="M6" t="inlineStr"/>
       <c r="N6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R6" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S6" t="n">
         <v>25</v>
@@ -1235,12 +1223,22 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2023-06-19</t>
+          <t>2023-07-15</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>19:30</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1249,7 +1247,6 @@
       <c r="AE6" t="b">
         <v>0</v>
       </c>
-      <c r="AF6" t="inlineStr"/>
       <c r="AG6" t="b">
         <v>0</v>
       </c>
@@ -1267,74 +1264,62 @@
       <c r="AY6" t="inlineStr"/>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110221107</t>
+          <t>https://artportalen.se/Sighting/110851317</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>110885428</v>
+        <v>109849948</v>
       </c>
       <c r="B7" t="n">
-        <v>110078</v>
+        <v>57890</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>220299</v>
+        <v>100082</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Svinrot</t>
+          <t>Röd glada</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Scorzonera humilis</t>
+          <t>Milvus milvus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>fullt utvecklade blad</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr"/>
       <c r="L7" t="inlineStr"/>
-      <c r="N7" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="M7" t="inlineStr"/>
+      <c r="N7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Kullen ö om, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>583671</v>
+        <v>583497</v>
       </c>
       <c r="R7" t="n">
-        <v>6528446</v>
+        <v>6528368</v>
       </c>
       <c r="S7" t="n">
-        <v>5</v>
+        <v>25</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1358,12 +1343,22 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-06-06</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>08:30</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1372,44 +1367,33 @@
       <c r="AE7" t="b">
         <v>0</v>
       </c>
-      <c r="AF7" t="inlineStr"/>
       <c r="AG7" t="b">
         <v>0</v>
-      </c>
-      <c r="AH7" t="inlineStr">
-        <is>
-          <t>Skogsmark</t>
-        </is>
-      </c>
-      <c r="AI7" t="inlineStr">
-        <is>
-          <t>blandskog</t>
-        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Bo Karlsson</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110885428</t>
+          <t>https://artportalen.se/Sighting/109849948</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>110234773</v>
+        <v>110392950</v>
       </c>
       <c r="B8" t="n">
-        <v>104628</v>
+        <v>57825</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1417,42 +1401,38 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>222412</v>
+        <v>100096</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Fiskgjuse</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pandion haliaetus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="K8" t="inlineStr"/>
       <c r="L8" t="inlineStr"/>
+      <c r="M8" t="inlineStr"/>
       <c r="N8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R8" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S8" t="n">
         <v>25</v>
@@ -1479,22 +1459,22 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2023-06-20</t>
+          <t>2023-06-26</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>16:24</t>
+          <t>17:00</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1503,7 +1483,6 @@
       <c r="AE8" t="b">
         <v>0</v>
       </c>
-      <c r="AF8" t="inlineStr"/>
       <c r="AG8" t="b">
         <v>0</v>
       </c>
@@ -1521,68 +1500,58 @@
       <c r="AY8" t="inlineStr"/>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110234773</t>
+          <t>https://artportalen.se/Sighting/110392950</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>110866072</v>
+        <v>110851372</v>
       </c>
       <c r="B9" t="n">
-        <v>104628</v>
+        <v>57860</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222412</v>
+        <v>100100</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Tibast</t>
+          <t>Bivråk</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Daphne mezereum</t>
+          <t>Pernis apivorus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="K9" t="inlineStr"/>
+      <c r="L9" t="inlineStr"/>
+      <c r="M9" t="inlineStr"/>
+      <c r="N9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Bergalund, Bergalund, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>583510</v>
+        <v>583497</v>
       </c>
       <c r="R9" t="n">
-        <v>6528549</v>
+        <v>6528368</v>
       </c>
       <c r="S9" t="n">
-        <v>1</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1606,22 +1575,22 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2023-07-16</t>
+          <t>2023-07-15</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>16:00</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1636,49 +1605,49 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Anna Sahlberg</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Anna Sahlberg</t>
+          <t>Daniel Franzén</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/110866072</t>
+          <t>https://artportalen.se/Sighting/110851372</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>111215642</v>
+        <v>110234764</v>
       </c>
       <c r="B10" t="n">
-        <v>101228</v>
+        <v>8882</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>222771</v>
+        <v>100890</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Svart trolldruva</t>
+          <t>Mulmknäppare</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Actaea spicata</t>
+          <t>Elater ferrugineus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
@@ -1687,12 +1656,9 @@
         </is>
       </c>
       <c r="J10" t="inlineStr"/>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+      <c r="K10" t="inlineStr"/>
       <c r="L10" t="inlineStr"/>
+      <c r="M10" t="inlineStr"/>
       <c r="N10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
@@ -1730,22 +1696,22 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-06-20</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>20:32</t>
+          <t>16:24</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1772,59 +1738,63 @@
       <c r="AY10" t="inlineStr"/>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/111215642</t>
+          <t>https://artportalen.se/Sighting/110234764</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>111215677</v>
+        <v>107325305</v>
       </c>
       <c r="B11" t="n">
-        <v>99154</v>
+        <v>57794</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>223619</v>
+        <v>102621</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ängsnattviol</t>
+          <t>Sparvuggla</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Platanthera bifolia subsp. bifolia</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr"/>
+          <t>Glaucidium passerinum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr"/>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>i frukt</t>
-        </is>
-      </c>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr"/>
       <c r="L11" t="inlineStr"/>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+          <t>Kullen Tegnebol, Srm</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>583651</v>
+        <v>583497</v>
       </c>
       <c r="R11" t="n">
-        <v>6528484</v>
+        <v>6528368</v>
       </c>
       <c r="S11" t="n">
         <v>25</v>
@@ -1851,22 +1821,22 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>2023-08-01</t>
+          <t>2023-03-16</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>20:35</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1875,7 +1845,6 @@
       <c r="AE11" t="b">
         <v>0</v>
       </c>
-      <c r="AF11" t="inlineStr"/>
       <c r="AG11" t="b">
         <v>0</v>
       </c>
@@ -1892,6 +1861,865 @@
       </c>
       <c r="AY11" t="inlineStr"/>
       <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/107325305</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>110234790</v>
+      </c>
+      <c r="B12" t="n">
+        <v>9414</v>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>105076</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Noshornsoxe</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Sinodendron cylindricum</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr"/>
+      <c r="K12" t="inlineStr"/>
+      <c r="L12" t="inlineStr"/>
+      <c r="M12" t="inlineStr"/>
+      <c r="N12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>583651</v>
+      </c>
+      <c r="R12" t="n">
+        <v>6528484</v>
+      </c>
+      <c r="S12" t="n">
+        <v>25</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF12" t="inlineStr"/>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110234790</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>110221107</v>
+      </c>
+      <c r="B13" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr"/>
+      <c r="K13" t="inlineStr"/>
+      <c r="L13" t="inlineStr"/>
+      <c r="N13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>583651</v>
+      </c>
+      <c r="R13" t="n">
+        <v>6528484</v>
+      </c>
+      <c r="S13" t="n">
+        <v>25</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2023-06-19</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF13" t="inlineStr"/>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110221107</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>110885428</v>
+      </c>
+      <c r="B14" t="n">
+        <v>110078</v>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220299</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Svinrot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Scorzonera humilis</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>fullt utvecklade blad</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr"/>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Kullen ö om, Srm</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>583671</v>
+      </c>
+      <c r="R14" t="n">
+        <v>6528446</v>
+      </c>
+      <c r="S14" t="n">
+        <v>5</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2023-07-16</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2023-07-16</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF14" t="inlineStr"/>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>Skogsmark</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>blandskog</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Bo Karlsson</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110885428</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>110234773</v>
+      </c>
+      <c r="B15" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr"/>
+      <c r="K15" t="inlineStr"/>
+      <c r="L15" t="inlineStr"/>
+      <c r="N15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>583651</v>
+      </c>
+      <c r="R15" t="n">
+        <v>6528484</v>
+      </c>
+      <c r="S15" t="n">
+        <v>25</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2023-06-20</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>16:24</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF15" t="inlineStr"/>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110234773</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>110866072</v>
+      </c>
+      <c r="B16" t="n">
+        <v>104628</v>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>222412</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Tibast</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Daphne mezereum</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Bergalund, Bergalund, Srm</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>583510</v>
+      </c>
+      <c r="R16" t="n">
+        <v>6528549</v>
+      </c>
+      <c r="S16" t="n">
+        <v>1</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2023-07-16</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2023-07-16</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Anna Sahlberg</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Anna Sahlberg</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/110866072</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>111215642</v>
+      </c>
+      <c r="B17" t="n">
+        <v>101228</v>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>222771</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Svart trolldruva</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Actaea spicata</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr"/>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr"/>
+      <c r="N17" t="inlineStr"/>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>583651</v>
+      </c>
+      <c r="R17" t="n">
+        <v>6528484</v>
+      </c>
+      <c r="S17" t="n">
+        <v>25</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>20:32</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF17" t="inlineStr"/>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111215642</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>111215677</v>
+      </c>
+      <c r="B18" t="n">
+        <v>99154</v>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>223619</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Ängsnattviol</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Platanthera bifolia subsp. bifolia</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr"/>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr"/>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>i frukt</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr"/>
+      <c r="N18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Skog Kullen Tegnebol, Kullen, Tegnebol, Srm</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>583651</v>
+      </c>
+      <c r="R18" t="n">
+        <v>6528484</v>
+      </c>
+      <c r="S18" t="n">
+        <v>25</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Katrineholm</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Björkvik</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2023-08-01</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>20:35</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF18" t="inlineStr"/>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Daniel Franzén</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/111215677</t>
         </is>
@@ -1909,6 +2737,13 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
